--- a/frontend/src/assets/files/sample.xlsx
+++ b/frontend/src/assets/files/sample.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\유현\개발\내문서\cau-fix-web\frontend\src\assests\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\유현\개발\내문서\cau-fix-web\frontend\src\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F91D51D-A556-4FAC-8CF3-ADD25E36A9D8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A830CCA-5A5A-492E-A064-B6AFC42EF96B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="105">
   <si>
     <t>번호</t>
   </si>
@@ -190,18 +190,9 @@
     <t>외래 접수 창구 PC에서 네트워크 속도가 느려 환자 접수 처리에 지연이 발생합니다.</t>
   </si>
   <si>
-    <t>시설팀 확인 후 제거 예정</t>
-  </si>
-  <si>
     <t>냉매 점검 및 수리 완료</t>
   </si>
   <si>
-    <t>부품 주문 후 재설치 진행 중</t>
-  </si>
-  <si>
-    <t>센서 교체 작업 진행 중</t>
-  </si>
-  <si>
     <t>온수 모듈 교체 완료</t>
   </si>
   <si>
@@ -268,24 +259,6 @@
     <t>중앙 복도</t>
   </si>
   <si>
-    <t>door_support.jpg</t>
-  </si>
-  <si>
-    <t>aircon.jpg</t>
-  </si>
-  <si>
-    <t>towel_holder.jpg</t>
-  </si>
-  <si>
-    <t>door_sensor.jpg</t>
-  </si>
-  <si>
-    <t>water_dispenser.jpg</t>
-  </si>
-  <si>
-    <t>corridor_light.jpg</t>
-  </si>
-  <si>
     <t>접수전</t>
   </si>
   <si>
@@ -379,6 +352,10 @@
   </si>
   <si>
     <t>전기/통신</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>aircon.png</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -792,6 +769,7 @@
   <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="6" max="6" width="15.75" customWidth="1"/>
     <col min="10" max="10" width="16.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -843,17 +821,11 @@
       <c r="E2" t="s">
         <v>41</v>
       </c>
-      <c r="F2" t="s">
-        <v>56</v>
-      </c>
       <c r="G2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H2" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="I2" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J2" s="2">
         <v>46082.375</v>
@@ -876,16 +848,16 @@
         <v>42</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H3" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="I3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J3" s="2">
         <v>46054.5</v>
@@ -907,17 +879,11 @@
       <c r="E4" t="s">
         <v>43</v>
       </c>
-      <c r="F4" t="s">
-        <v>58</v>
-      </c>
       <c r="G4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="I4" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J4" s="2">
         <v>46054.625</v>
@@ -939,17 +905,11 @@
       <c r="E5" t="s">
         <v>44</v>
       </c>
-      <c r="F5" t="s">
-        <v>59</v>
-      </c>
       <c r="G5" t="s">
-        <v>67</v>
-      </c>
-      <c r="H5" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="I5" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J5" s="2">
         <v>46082.75</v>
@@ -972,16 +932,13 @@
         <v>45</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G6" t="s">
-        <v>68</v>
-      </c>
-      <c r="H6" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="I6" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J6" s="2">
         <v>46082.875</v>
@@ -1004,16 +961,13 @@
         <v>46</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G7" t="s">
-        <v>69</v>
-      </c>
-      <c r="H7" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="I7" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J7" s="2">
         <v>46024</v>
@@ -1030,16 +984,16 @@
         <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="G8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I8" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J8" s="2">
         <v>46030.032638888886</v>
@@ -1053,19 +1007,19 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="G9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I9" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J9" s="2">
         <v>45728.032638888886</v>
@@ -1082,16 +1036,16 @@
         <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="G10" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I10" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J10" s="2">
         <v>45727.032638888886</v>
@@ -1108,16 +1062,16 @@
         <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E11" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="G11" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="I11" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J11" s="2">
         <v>45699.032638888886</v>
@@ -1134,16 +1088,16 @@
         <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E12" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="G12" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I12" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J12" s="2">
         <v>45700.032638888886</v>
@@ -1160,19 +1114,19 @@
         <v>22</v>
       </c>
       <c r="D13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" t="s">
         <v>97</v>
       </c>
-      <c r="E13" t="s">
-        <v>106</v>
-      </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G13" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I13" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J13" s="2">
         <v>45701.032638888886</v>
@@ -1189,16 +1143,16 @@
         <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="E14" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="G14" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="I14" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J14" s="2">
         <v>45361.032638888886</v>
@@ -1215,19 +1169,19 @@
         <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E15" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="F15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G15" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I15" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J15" s="2">
         <v>45360.032638888886</v>
@@ -1244,19 +1198,19 @@
         <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E16" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="I16" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J16" s="2">
         <v>45331.032638888886</v>
@@ -1273,19 +1227,19 @@
         <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="E17" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="F17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I17" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J17" s="2">
         <v>45330.032638888886</v>
@@ -1308,10 +1262,10 @@
         <v>47</v>
       </c>
       <c r="G18" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I18" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J18" s="2">
         <v>45332.03402777778</v>
@@ -1334,13 +1288,13 @@
         <v>48</v>
       </c>
       <c r="F19" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G19" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I19" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J19" s="2">
         <v>45329.03402777778</v>
@@ -1363,10 +1317,10 @@
         <v>49</v>
       </c>
       <c r="G20" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I20" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J20" s="2">
         <v>45303.03402777778</v>
@@ -1389,10 +1343,10 @@
         <v>50</v>
       </c>
       <c r="G21" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I21" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J21" s="2">
         <v>45304.03402777778</v>
@@ -1415,10 +1369,10 @@
         <v>51</v>
       </c>
       <c r="G22" t="s">
+        <v>76</v>
+      </c>
+      <c r="I22" t="s">
         <v>79</v>
-      </c>
-      <c r="I22" t="s">
-        <v>88</v>
       </c>
       <c r="J22" s="2">
         <v>45297.03402777778</v>
@@ -1441,10 +1395,10 @@
         <v>52</v>
       </c>
       <c r="G23" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I23" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J23" s="2">
         <v>45301.03402777778</v>
@@ -1467,10 +1421,10 @@
         <v>53</v>
       </c>
       <c r="G24" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I24" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J24" s="2">
         <v>45301.03402777778</v>
@@ -1493,10 +1447,10 @@
         <v>54</v>
       </c>
       <c r="G25" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I25" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J25" s="2">
         <v>45301.03402777778</v>
@@ -1519,10 +1473,10 @@
         <v>55</v>
       </c>
       <c r="G26" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I26" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J26" s="2">
         <v>46090.03402777778</v>

--- a/frontend/src/assets/files/sample.xlsx
+++ b/frontend/src/assets/files/sample.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\유현\개발\내문서\cau-fix-web\frontend\src\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A830CCA-5A5A-492E-A064-B6AFC42EF96B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7571711D-6AB6-4247-8462-014C99BEE946}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="민원" sheetId="1" r:id="rId1"/>
+    <sheet name="처리" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="118">
   <si>
     <t>번호</t>
   </si>
@@ -357,13 +358,69 @@
   <si>
     <t>aircon.png</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>번호</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>처리자</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이중앙</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>오관리</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>한병원</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>김시설</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>최전기</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>박점검</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>점검 완료</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>강통신</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>윤보안</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-02-28  15:47:00 PM</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>처리시간</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="178" formatCode="[$-409]yy&quot;-&quot;m&quot;-&quot;d\ h:mm\ AM/PM;@"/>
+    <numFmt numFmtId="179" formatCode="[$-409]yyyy&quot;-&quot;m&quot;-&quot;d\ h:mm\ AM/PM;@"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -381,6 +438,21 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -422,12 +494,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -766,14 +853,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="6" width="15.75" customWidth="1"/>
-    <col min="10" max="10" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -790,22 +876,19 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -821,17 +904,17 @@
       <c r="E2" t="s">
         <v>41</v>
       </c>
-      <c r="G2" t="s">
+      <c r="F2" t="s">
         <v>61</v>
       </c>
-      <c r="I2" t="s">
+      <c r="H2" t="s">
         <v>79</v>
       </c>
-      <c r="J2" s="2">
+      <c r="I2" s="2">
         <v>46082.375</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -848,22 +931,19 @@
         <v>42</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G3" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="H3" t="s">
-        <v>104</v>
-      </c>
-      <c r="I3" t="s">
         <v>80</v>
       </c>
-      <c r="J3" s="2">
+      <c r="I3" s="2">
         <v>46054.5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -879,17 +959,17 @@
       <c r="E4" t="s">
         <v>43</v>
       </c>
-      <c r="G4" t="s">
+      <c r="F4" t="s">
         <v>63</v>
       </c>
-      <c r="I4" t="s">
+      <c r="H4" t="s">
         <v>81</v>
       </c>
-      <c r="J4" s="2">
+      <c r="I4" s="2">
         <v>46054.625</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -905,17 +985,17 @@
       <c r="E5" t="s">
         <v>44</v>
       </c>
-      <c r="G5" t="s">
+      <c r="F5" t="s">
         <v>64</v>
       </c>
-      <c r="I5" t="s">
+      <c r="H5" t="s">
         <v>81</v>
       </c>
-      <c r="J5" s="2">
+      <c r="I5" s="2">
         <v>46082.75</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -932,19 +1012,16 @@
         <v>45</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
-      </c>
-      <c r="G6" t="s">
         <v>65</v>
       </c>
-      <c r="I6" t="s">
+      <c r="H6" t="s">
         <v>80</v>
       </c>
-      <c r="J6" s="2">
+      <c r="I6" s="2">
         <v>46082.875</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -961,19 +1038,16 @@
         <v>46</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
-      </c>
-      <c r="G7" t="s">
         <v>66</v>
       </c>
-      <c r="I7" t="s">
+      <c r="H7" t="s">
         <v>80</v>
       </c>
-      <c r="J7" s="2">
+      <c r="I7" s="2">
         <v>46024</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -989,17 +1063,17 @@
       <c r="E8" t="s">
         <v>102</v>
       </c>
-      <c r="G8" t="s">
+      <c r="F8" t="s">
         <v>67</v>
       </c>
-      <c r="I8" t="s">
+      <c r="H8" t="s">
         <v>82</v>
       </c>
-      <c r="J8" s="2">
+      <c r="I8" s="2">
         <v>46030.032638888886</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1015,17 +1089,17 @@
       <c r="E9" t="s">
         <v>101</v>
       </c>
-      <c r="G9" t="s">
+      <c r="F9" t="s">
         <v>68</v>
       </c>
-      <c r="I9" t="s">
+      <c r="H9" t="s">
         <v>82</v>
       </c>
-      <c r="J9" s="2">
+      <c r="I9" s="2">
         <v>45728.032638888886</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1041,17 +1115,17 @@
       <c r="E10" t="s">
         <v>100</v>
       </c>
-      <c r="G10" t="s">
+      <c r="F10" t="s">
         <v>68</v>
       </c>
-      <c r="I10" t="s">
+      <c r="H10" t="s">
         <v>82</v>
       </c>
-      <c r="J10" s="2">
+      <c r="I10" s="2">
         <v>45727.032638888886</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1067,17 +1141,17 @@
       <c r="E11" t="s">
         <v>99</v>
       </c>
-      <c r="G11" t="s">
+      <c r="F11" t="s">
         <v>69</v>
       </c>
-      <c r="I11" t="s">
+      <c r="H11" t="s">
         <v>82</v>
       </c>
-      <c r="J11" s="2">
+      <c r="I11" s="2">
         <v>45699.032638888886</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1093,17 +1167,17 @@
       <c r="E12" t="s">
         <v>98</v>
       </c>
-      <c r="G12" t="s">
+      <c r="F12" t="s">
         <v>70</v>
       </c>
-      <c r="I12" t="s">
+      <c r="H12" t="s">
         <v>81</v>
       </c>
-      <c r="J12" s="2">
+      <c r="I12" s="2">
         <v>45700.032638888886</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1120,19 +1194,16 @@
         <v>97</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G13" t="s">
         <v>70</v>
       </c>
-      <c r="I13" t="s">
+      <c r="H13" t="s">
         <v>80</v>
       </c>
-      <c r="J13" s="2">
+      <c r="I13" s="2">
         <v>45701.032638888886</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1148,17 +1219,17 @@
       <c r="E14" t="s">
         <v>96</v>
       </c>
-      <c r="G14" t="s">
+      <c r="F14" t="s">
         <v>69</v>
       </c>
-      <c r="I14" t="s">
+      <c r="H14" t="s">
         <v>81</v>
       </c>
-      <c r="J14" s="2">
+      <c r="I14" s="2">
         <v>45361.032638888886</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1175,19 +1246,16 @@
         <v>95</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
-      </c>
-      <c r="G15" t="s">
         <v>71</v>
       </c>
-      <c r="I15" t="s">
+      <c r="H15" t="s">
         <v>80</v>
       </c>
-      <c r="J15" s="2">
+      <c r="I15" s="2">
         <v>45360.032638888886</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1204,19 +1272,16 @@
         <v>94</v>
       </c>
       <c r="F16" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16" t="s">
         <v>69</v>
       </c>
-      <c r="I16" t="s">
+      <c r="H16" t="s">
         <v>80</v>
       </c>
-      <c r="J16" s="2">
+      <c r="I16" s="2">
         <v>45331.032638888886</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1233,19 +1298,16 @@
         <v>93</v>
       </c>
       <c r="F17" t="s">
-        <v>59</v>
-      </c>
-      <c r="G17" t="s">
         <v>67</v>
       </c>
-      <c r="I17" t="s">
+      <c r="H17" t="s">
         <v>80</v>
       </c>
-      <c r="J17" s="2">
+      <c r="I17" s="2">
         <v>45330.032638888886</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1261,17 +1323,17 @@
       <c r="E18" t="s">
         <v>47</v>
       </c>
-      <c r="G18" t="s">
+      <c r="F18" t="s">
         <v>72</v>
       </c>
-      <c r="I18" t="s">
+      <c r="H18" t="s">
         <v>79</v>
       </c>
-      <c r="J18" s="2">
+      <c r="I18" s="2">
         <v>45332.03402777778</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1288,19 +1350,16 @@
         <v>48</v>
       </c>
       <c r="F19" t="s">
-        <v>60</v>
-      </c>
-      <c r="G19" t="s">
         <v>73</v>
       </c>
-      <c r="I19" t="s">
+      <c r="H19" t="s">
         <v>80</v>
       </c>
-      <c r="J19" s="2">
+      <c r="I19" s="2">
         <v>45329.03402777778</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1316,17 +1375,17 @@
       <c r="E20" t="s">
         <v>49</v>
       </c>
-      <c r="G20" t="s">
+      <c r="F20" t="s">
         <v>74</v>
       </c>
-      <c r="I20" t="s">
+      <c r="H20" t="s">
         <v>82</v>
       </c>
-      <c r="J20" s="2">
+      <c r="I20" s="2">
         <v>45303.03402777778</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1342,17 +1401,17 @@
       <c r="E21" t="s">
         <v>50</v>
       </c>
-      <c r="G21" t="s">
+      <c r="F21" t="s">
         <v>75</v>
       </c>
-      <c r="I21" t="s">
+      <c r="H21" t="s">
         <v>79</v>
       </c>
-      <c r="J21" s="2">
+      <c r="I21" s="2">
         <v>45304.03402777778</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1368,17 +1427,17 @@
       <c r="E22" t="s">
         <v>51</v>
       </c>
-      <c r="G22" t="s">
+      <c r="F22" t="s">
         <v>76</v>
       </c>
-      <c r="I22" t="s">
+      <c r="H22" t="s">
         <v>79</v>
       </c>
-      <c r="J22" s="2">
+      <c r="I22" s="2">
         <v>45297.03402777778</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1394,17 +1453,17 @@
       <c r="E23" t="s">
         <v>52</v>
       </c>
-      <c r="G23" t="s">
+      <c r="F23" t="s">
         <v>73</v>
       </c>
-      <c r="I23" t="s">
+      <c r="H23" t="s">
         <v>82</v>
       </c>
-      <c r="J23" s="2">
+      <c r="I23" s="2">
         <v>45301.03402777778</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1420,17 +1479,17 @@
       <c r="E24" t="s">
         <v>53</v>
       </c>
-      <c r="G24" t="s">
+      <c r="F24" t="s">
         <v>77</v>
       </c>
-      <c r="I24" t="s">
+      <c r="H24" t="s">
         <v>82</v>
       </c>
-      <c r="J24" s="2">
+      <c r="I24" s="2">
         <v>45301.03402777778</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1446,17 +1505,17 @@
       <c r="E25" t="s">
         <v>54</v>
       </c>
-      <c r="G25" t="s">
+      <c r="F25" t="s">
         <v>77</v>
       </c>
-      <c r="I25" t="s">
+      <c r="H25" t="s">
         <v>82</v>
       </c>
-      <c r="J25" s="2">
+      <c r="I25" s="2">
         <v>45301.03402777778</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1472,15 +1531,318 @@
       <c r="E26" t="s">
         <v>55</v>
       </c>
-      <c r="G26" t="s">
+      <c r="F26" t="s">
         <v>78</v>
       </c>
-      <c r="I26" t="s">
+      <c r="H26" t="s">
         <v>79</v>
       </c>
-      <c r="J26" s="2">
+      <c r="I26" s="2">
         <v>46090.03402777778</v>
       </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{011A9EEE-03A3-4373-97D5-C87F85303DEA}">
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="31.125" style="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" s="9">
+        <v>46055.5</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="5"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C6" s="7">
+        <v>46091.875</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="6">
+        <v>46025</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C11" s="6"/>
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C13" s="6">
+        <v>45703.449305555558</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" s="7">
+        <v>45361.490972222222</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" s="7">
+        <v>45333.407638888886</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="6"/>
+      <c r="D18" s="5"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="6">
+        <v>45330.03402777778</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="5"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" s="6"/>
+      <c r="D22" s="5"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" s="6"/>
+      <c r="D23" s="5"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C24" s="6"/>
+      <c r="D24" s="5"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C25" s="6"/>
+      <c r="D25" s="5"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/frontend/src/assets/files/sample.xlsx
+++ b/frontend/src/assets/files/sample.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\유현\개발\내문서\cau-fix-web\frontend\src\assets\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\유현\개발\시설관리팀\내문서\cau-fix-web\frontend\src\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7571711D-6AB6-4247-8462-014C99BEE946}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAFC2AD8-3BE3-46CB-BAD8-C6767E310758}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="민원" sheetId="1" r:id="rId1"/>
@@ -21,10 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="118">
-  <si>
-    <t>번호</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="124">
   <si>
     <t>부서</t>
   </si>
@@ -410,15 +407,42 @@
   <si>
     <t>처리시간</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>디지털전략팀</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기계/소방</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>접수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>본관</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>엘리베이터 고장</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4호기 문이 안열립니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>번호</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="178" formatCode="[$-409]yy&quot;-&quot;m&quot;-&quot;d\ h:mm\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="[$-409]yyyy&quot;-&quot;m&quot;-&quot;d\ h:mm\ AM/PM;@"/>
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="[$-409]yy&quot;-&quot;m&quot;-&quot;d\ h:mm\ AM/PM;@"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -494,7 +518,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -507,14 +531,11 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -853,39 +874,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="4" max="4" width="18.75" customWidth="1"/>
     <col min="9" max="9" width="16.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -893,22 +915,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I2" s="2">
         <v>46082.375</v>
@@ -919,28 +941,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I3" s="2">
-        <v>46054.5</v>
+        <v>46124.5</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -948,22 +970,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I4" s="2">
         <v>46054.625</v>
@@ -974,22 +996,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I5" s="2">
         <v>46082.75</v>
@@ -1000,22 +1022,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I6" s="2">
         <v>46082.875</v>
@@ -1026,22 +1048,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I7" s="2">
         <v>46024</v>
@@ -1052,22 +1074,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I8" s="2">
         <v>46030.032638888886</v>
@@ -1078,22 +1100,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I9" s="2">
         <v>45728.032638888886</v>
@@ -1104,22 +1126,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I10" s="2">
         <v>45727.032638888886</v>
@@ -1130,22 +1152,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I11" s="2">
         <v>45699.032638888886</v>
@@ -1156,22 +1178,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I12" s="2">
         <v>45700.032638888886</v>
@@ -1182,22 +1204,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I13" s="2">
         <v>45701.032638888886</v>
@@ -1208,22 +1230,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I14" s="2">
         <v>45361.032638888886</v>
@@ -1234,22 +1256,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I15" s="2">
         <v>45360.032638888886</v>
@@ -1260,22 +1282,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I16" s="2">
         <v>45331.032638888886</v>
@@ -1286,22 +1308,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D17" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" t="s">
         <v>92</v>
       </c>
-      <c r="E17" t="s">
-        <v>93</v>
-      </c>
       <c r="F17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I17" s="2">
         <v>45330.032638888886</v>
@@ -1312,22 +1334,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I18" s="2">
         <v>45332.03402777778</v>
@@ -1338,22 +1360,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I19" s="2">
         <v>45329.03402777778</v>
@@ -1364,22 +1386,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I20" s="2">
         <v>45303.03402777778</v>
@@ -1390,22 +1412,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I21" s="2">
         <v>45304.03402777778</v>
@@ -1416,22 +1438,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I22" s="2">
         <v>45297.03402777778</v>
@@ -1442,22 +1464,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I23" s="2">
         <v>45301.03402777778</v>
@@ -1468,22 +1490,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I24" s="2">
         <v>45301.03402777778</v>
@@ -1494,22 +1516,22 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I25" s="2">
         <v>45301.03402777778</v>
@@ -1520,25 +1542,51 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F26" t="s">
+        <v>77</v>
+      </c>
+      <c r="H26" t="s">
         <v>78</v>
       </c>
-      <c r="H26" t="s">
-        <v>79</v>
-      </c>
       <c r="I26" s="2">
-        <v>46090.03402777778</v>
+        <v>46091.03402777778</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C27" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" t="s">
+        <v>122</v>
+      </c>
+      <c r="F27" t="s">
+        <v>120</v>
+      </c>
+      <c r="H27" t="s">
+        <v>119</v>
+      </c>
+      <c r="I27" s="2">
+        <v>46120.625</v>
       </c>
     </row>
   </sheetData>
@@ -1558,16 +1606,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="C1" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -1583,13 +1631,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C3" s="9">
-        <v>46055.5</v>
+        <v>106</v>
+      </c>
+      <c r="C3" s="2">
+        <v>46125.5</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1597,7 +1645,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="5"/>
@@ -1607,7 +1655,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="5"/>
@@ -1617,13 +1665,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C6" s="7">
         <v>46091.875</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -1631,13 +1679,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C7" s="6">
         <v>46025</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -1645,7 +1693,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="5"/>
@@ -1655,7 +1703,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="5"/>
@@ -1665,7 +1713,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5"/>
@@ -1675,7 +1723,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="5"/>
@@ -1685,7 +1733,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5"/>
@@ -1695,13 +1743,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C13" s="6">
         <v>45703.449305555558</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -1709,7 +1757,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5"/>
@@ -1719,13 +1767,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C15" s="7">
         <v>45361.490972222222</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -1733,13 +1781,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C16" s="7">
         <v>45333.407638888886</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -1747,13 +1795,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>116</v>
-      </c>
       <c r="D17" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -1761,7 +1809,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5"/>
@@ -1771,13 +1819,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C19" s="6">
         <v>45330.03402777778</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -1801,7 +1849,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5"/>
@@ -1811,7 +1859,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="5"/>
@@ -1821,7 +1869,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5"/>
@@ -1831,7 +1879,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="5"/>

--- a/frontend/src/assets/files/sample.xlsx
+++ b/frontend/src/assets/files/sample.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30006"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\유현\개발\시설관리팀\내문서\cau-fix-web\frontend\src\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAFC2AD8-3BE3-46CB-BAD8-C6767E310758}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{BAFC2AD8-3BE3-46CB-BAD8-C6767E310758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09D877EC-EC2C-4EED-A52A-12E810F78412}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,13 +16,33 @@
     <sheet name="민원" sheetId="1" r:id="rId1"/>
     <sheet name="처리" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="124">
   <si>
+    <t>번호</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>부서</t>
   </si>
   <si>
@@ -35,9 +55,6 @@
     <t>민원 내용</t>
   </si>
   <si>
-    <t>처리 내용</t>
-  </si>
-  <si>
     <t>장소</t>
   </si>
   <si>
@@ -53,307 +70,316 @@
     <t>시설관리팀</t>
   </si>
   <si>
+    <t>건축/영선</t>
+  </si>
+  <si>
+    <t>출입문 지지대 제거 요청</t>
+  </si>
+  <si>
+    <t>출입문 하단 지지대가 통행에 방해되어 제거 요청</t>
+  </si>
+  <si>
+    <t>본관 1층 출입구</t>
+  </si>
+  <si>
+    <t>접수전</t>
+  </si>
+  <si>
+    <t>기계/소방</t>
+  </si>
+  <si>
+    <t>에어컨 고장</t>
+  </si>
+  <si>
+    <t>회의실 에어컨이 작동하지 않음</t>
+  </si>
+  <si>
+    <t>본관 3층 회의실</t>
+  </si>
+  <si>
+    <t>aircon.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>완료</t>
+  </si>
+  <si>
     <t>총무팀</t>
   </si>
   <si>
+    <t>미화</t>
+  </si>
+  <si>
+    <t>화장실 수건 걸이 탈락</t>
+  </si>
+  <si>
+    <t>화장실 벽면 수건 걸이가 떨어짐</t>
+  </si>
+  <si>
+    <t>본관 2층 화장실</t>
+  </si>
+  <si>
+    <t>진행중</t>
+  </si>
+  <si>
+    <t>보안</t>
+  </si>
+  <si>
+    <t>자동문 센서 고장</t>
+  </si>
+  <si>
+    <t>자동문이 사람 인식이 잘 되지 않음</t>
+  </si>
+  <si>
+    <t>본관 1층 로비</t>
+  </si>
+  <si>
     <t>복지팀</t>
   </si>
   <si>
+    <t>장비(PC)</t>
+  </si>
+  <si>
+    <t>정수기 온수 장치 고장</t>
+  </si>
+  <si>
+    <t>정수기에서 온수가 나오지 않음</t>
+  </si>
+  <si>
+    <t>별관 2층 휴게실</t>
+  </si>
+  <si>
+    <t>전기/통신</t>
+  </si>
+  <si>
+    <t>복도 조명 교체 요청</t>
+  </si>
+  <si>
+    <t>복도 조명이 깜빡이며 수명이 다함</t>
+  </si>
+  <si>
+    <t>본관 2층 복도</t>
+  </si>
+  <si>
+    <t>네트워크</t>
+  </si>
+  <si>
+    <t>응급실 자동문 개폐 지연</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>응급실 출입 자동문이 환자 침대 이동 시 반응이 늦어 충돌 위험이 있습니다. 센서 감도 및 모터 상태 점검이 필요합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>연구동</t>
+  </si>
+  <si>
+    <t>접수</t>
+  </si>
+  <si>
     <t>관리팀</t>
   </si>
   <si>
+    <t>전기/통신</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3병동 복도 조명 불량</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3병동 복도 일부 LED 조명이 점등되지 않아 야간 근무 시 시야 확보가 어렵습니다. 조명 교체 요청드립니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>본관 1층</t>
+  </si>
+  <si>
+    <t>설비</t>
+  </si>
+  <si>
+    <t>MRI 장비실 냉방 온도 상승</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MRI 장비실 내부 온도가 기준치보다 높게 유지되고 있습니다. 장비 보호를 위해 냉방기 작동 상태 점검 바랍니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지하주차장 배수 불량</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지하주차장 B2 구역 배수구 주변에 물이 고여 차량 통행 시 미끄럼 위험이 있습니다. 배수관 막힘 여부 확인 요청드립니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>강의실 B</t>
+  </si>
+  <si>
+    <t>환경</t>
+  </si>
+  <si>
+    <t>2병동 화재감지기 오작동</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2병동 복도 화재감지기가 실제 화재 상황이 아님에도 경보가 발생했습니다. 감지기 점검 및 재설정 필요합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>강의실 A</t>
+  </si>
+  <si>
+    <t>외래 대기실 CCTV 화면 끊김</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>외래 대기실 CCTV 모니터 화면이 간헐적으로 끊겨 보안 모니터링이 어려운 상황입니다. 네트워크 연결 상태 확인 요청드립니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전기</t>
+  </si>
+  <si>
+    <t>수술실 콘센트 전원 불안정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>수술실 벽면 의료장비용 콘센트에서 전원이 간헐적으로 끊기는 현상이 발생합니다. 전기 라인 점검 필요합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>전산팀</t>
   </si>
   <si>
+    <t>병동 화장실 환풍기 소음 발생</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4병동 화장실 환풍기에서 지속적인 소음이 발생하여 환자들이 불편을 호소하고 있습니다. 베어링 또는 모터 점검 바랍니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>본관 2층</t>
+  </si>
+  <si>
+    <t>외래 접수 PC 네트워크 지연</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>외래 접수 창구 PC에서 EMR 접속 시 네트워크 속도가 느려 환자 접수 시간이 지연되고 있습니다. 네트워크 점검 요청드립니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>병원 로비 바닥 청소 상태 불량</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>병원 로비 바닥에 얼룩과 물자국이 남아 있어 미관이 좋지 않습니다. 미화팀 재정비 및 청소 요청드립니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>응급실 자동문 센서 오작동</t>
+  </si>
+  <si>
+    <t>응급실 출입구 자동문이 환자 이동 시 제대로 열리지 않아 충돌 위험이 있습니다. 센서 점검 요청드립니다.</t>
+  </si>
+  <si>
+    <t>수술실</t>
+  </si>
+  <si>
     <t>시설팀</t>
   </si>
   <si>
-    <t>건축영선</t>
+    <t>병동 복도 형광등 깜빡임</t>
+  </si>
+  <si>
+    <t>3병동 복도 형광등이 지속적으로 깜빡여 야간 근무 시 시야 확보가 어렵습니다. 전기 점검 필요합니다.</t>
+  </si>
+  <si>
+    <t>영상의학과</t>
+  </si>
+  <si>
+    <t>MRI 장비실 냉방 이상</t>
+  </si>
+  <si>
+    <t>MRI 장비실 내부 온도가 높아 장비 보호를 위해 냉방 장치 점검이 필요합니다.</t>
+  </si>
+  <si>
+    <t>응급실</t>
+  </si>
+  <si>
+    <t>지하 주차장 배수구 막힘</t>
+  </si>
+  <si>
+    <t>폭우 이후 지하 주차장 배수구가 막혀 물이 고이고 있습니다. 배수 정비 요청드립니다.</t>
+  </si>
+  <si>
+    <t>지하 주차장</t>
+  </si>
+  <si>
+    <t>병동 화재감지기 경보 오작동</t>
+  </si>
+  <si>
+    <t>2병동 화재감지기가 반복적으로 오작동하며 경보가 울리고 있습니다. 소방 설비 점검 필요합니다.</t>
+  </si>
+  <si>
+    <t>3병동</t>
+  </si>
+  <si>
+    <t>외래 대기실 CCTV 화면 끊김</t>
+  </si>
+  <si>
+    <t>외래 대기실 CCTV 모니터링 화면이 간헐적으로 끊겨 보안 확인이 어렵습니다.</t>
+  </si>
+  <si>
+    <t>수술실 전원 콘센트 불량</t>
+  </si>
+  <si>
+    <t>수술실 벽면 콘센트 일부에서 전원이 불안정하게 공급됩니다. 안전 점검 요청드립니다.</t>
+  </si>
+  <si>
+    <t>병원 로비</t>
+  </si>
+  <si>
+    <t>병동 화장실 환풍기 소음</t>
+  </si>
+  <si>
+    <t>환풍기에서 심한 소음이 발생하여 환자들이 불편을 호소하고 있습니다.</t>
+  </si>
+  <si>
+    <t>외래 접수 PC 네트워크 지연</t>
+  </si>
+  <si>
+    <t>외래 접수 창구 PC에서 네트워크 속도가 느려 환자 접수 처리에 지연이 발생합니다.</t>
+  </si>
+  <si>
+    <t>중앙 복도</t>
+  </si>
+  <si>
+    <t>디지털전략팀</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>기계/소방</t>
-  </si>
-  <si>
-    <t>미화</t>
-  </si>
-  <si>
-    <t>보안</t>
-  </si>
-  <si>
-    <t>장비(의료, PC)</t>
-  </si>
-  <si>
-    <t>전기/통신</t>
-  </si>
-  <si>
-    <t>네트워크</t>
-  </si>
-  <si>
-    <t>전기</t>
-  </si>
-  <si>
-    <t>설비</t>
-  </si>
-  <si>
-    <t>환경</t>
-  </si>
-  <si>
-    <t>출입문 지지대 제거 요청</t>
-  </si>
-  <si>
-    <t>에어컨 고장</t>
-  </si>
-  <si>
-    <t>화장실 수건 걸이 탈락</t>
-  </si>
-  <si>
-    <t>자동문 센서 고장</t>
-  </si>
-  <si>
-    <t>정수기 온수 장치 고장</t>
-  </si>
-  <si>
-    <t>복도 조명 교체 요청</t>
-  </si>
-  <si>
-    <t>응급실 자동문 센서 오작동</t>
-  </si>
-  <si>
-    <t>병동 복도 형광등 깜빡임</t>
-  </si>
-  <si>
-    <t>MRI 장비실 냉방 이상</t>
-  </si>
-  <si>
-    <t>지하 주차장 배수구 막힘</t>
-  </si>
-  <si>
-    <t>병동 화재감지기 경보 오작동</t>
-  </si>
-  <si>
-    <t>외래 대기실 CCTV 화면 끊김</t>
-  </si>
-  <si>
-    <t>수술실 전원 콘센트 불량</t>
-  </si>
-  <si>
-    <t>병동 화장실 환풍기 소음</t>
-  </si>
-  <si>
-    <t>외래 접수 PC 네트워크 지연</t>
-  </si>
-  <si>
-    <t>출입문 하단 지지대가 통행에 방해되어 제거 요청</t>
-  </si>
-  <si>
-    <t>회의실 에어컨이 작동하지 않음</t>
-  </si>
-  <si>
-    <t>화장실 벽면 수건 걸이가 떨어짐</t>
-  </si>
-  <si>
-    <t>자동문이 사람 인식이 잘 되지 않음</t>
-  </si>
-  <si>
-    <t>정수기에서 온수가 나오지 않음</t>
-  </si>
-  <si>
-    <t>복도 조명이 깜빡이며 수명이 다함</t>
-  </si>
-  <si>
-    <t>응급실 출입구 자동문이 환자 이동 시 제대로 열리지 않아 충돌 위험이 있습니다. 센서 점검 요청드립니다.</t>
-  </si>
-  <si>
-    <t>3병동 복도 형광등이 지속적으로 깜빡여 야간 근무 시 시야 확보가 어렵습니다. 전기 점검 필요합니다.</t>
-  </si>
-  <si>
-    <t>MRI 장비실 내부 온도가 높아 장비 보호를 위해 냉방 장치 점검이 필요합니다.</t>
-  </si>
-  <si>
-    <t>폭우 이후 지하 주차장 배수구가 막혀 물이 고이고 있습니다. 배수 정비 요청드립니다.</t>
-  </si>
-  <si>
-    <t>2병동 화재감지기가 반복적으로 오작동하며 경보가 울리고 있습니다. 소방 설비 점검 필요합니다.</t>
-  </si>
-  <si>
-    <t>외래 대기실 CCTV 모니터링 화면이 간헐적으로 끊겨 보안 확인이 어렵습니다.</t>
-  </si>
-  <si>
-    <t>수술실 벽면 콘센트 일부에서 전원이 불안정하게 공급됩니다. 안전 점검 요청드립니다.</t>
-  </si>
-  <si>
-    <t>환풍기에서 심한 소음이 발생하여 환자들이 불편을 호소하고 있습니다.</t>
-  </si>
-  <si>
-    <t>외래 접수 창구 PC에서 네트워크 속도가 느려 환자 접수 처리에 지연이 발생합니다.</t>
-  </si>
-  <si>
-    <t>냉매 점검 및 수리 완료</t>
-  </si>
-  <si>
-    <t>온수 모듈 교체 완료</t>
-  </si>
-  <si>
-    <t>LED 조명으로 교체 완료</t>
-  </si>
-  <si>
-    <t>점검 완료</t>
-  </si>
-  <si>
-    <t>점검 및 조치 완료</t>
-  </si>
-  <si>
-    <t>본관 1층 출입구</t>
-  </si>
-  <si>
-    <t>본관 3층 회의실</t>
-  </si>
-  <si>
-    <t>본관 2층 화장실</t>
-  </si>
-  <si>
-    <t>본관 1층 로비</t>
-  </si>
-  <si>
-    <t>별관 2층 휴게실</t>
-  </si>
-  <si>
-    <t>본관 2층 복도</t>
-  </si>
-  <si>
-    <t>연구동</t>
-  </si>
-  <si>
-    <t>본관 1층</t>
-  </si>
-  <si>
-    <t>강의실 B</t>
-  </si>
-  <si>
-    <t>강의실 A</t>
-  </si>
-  <si>
-    <t>본관 2층</t>
-  </si>
-  <si>
-    <t>수술실</t>
-  </si>
-  <si>
-    <t>영상의학과</t>
-  </si>
-  <si>
-    <t>응급실</t>
-  </si>
-  <si>
-    <t>지하 주차장</t>
-  </si>
-  <si>
-    <t>3병동</t>
-  </si>
-  <si>
-    <t>병원 로비</t>
-  </si>
-  <si>
-    <t>중앙 복도</t>
-  </si>
-  <si>
-    <t>접수전</t>
-  </si>
-  <si>
-    <t>완료</t>
-  </si>
-  <si>
-    <t>진행중</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>엘리베이터 고장</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4호기 문이 안열립니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>본관</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>접수</t>
-  </si>
-  <si>
-    <t>응급실 자동문 개폐 지연</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>3병동 복도 조명 불량</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MRI 장비실 냉방 온도 상승</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>지하주차장 배수 불량</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2병동 화재감지기 오작동</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>외래 대기실 CCTV 화면 끊김</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>수술실 콘센트 전원 불안정</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>병동 화장실 환풍기 소음 발생</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>외래 접수 PC 네트워크 지연</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>병원 로비 바닥 청소 상태 불량</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>병원 로비 바닥에 얼룩과 물자국이 남아 있어 미관이 좋지 않습니다. 미화팀 재정비 및 청소 요청드립니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>외래 접수 창구 PC에서 EMR 접속 시 네트워크 속도가 느려 환자 접수 시간이 지연되고 있습니다. 네트워크 점검 요청드립니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>4병동 화장실 환풍기에서 지속적인 소음이 발생하여 환자들이 불편을 호소하고 있습니다. 베어링 또는 모터 점검 바랍니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>수술실 벽면 의료장비용 콘센트에서 전원이 간헐적으로 끊기는 현상이 발생합니다. 전기 라인 점검 필요합니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>외래 대기실 CCTV 모니터 화면이 간헐적으로 끊겨 보안 모니터링이 어려운 상황입니다. 네트워크 연결 상태 확인 요청드립니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2병동 복도 화재감지기가 실제 화재 상황이 아님에도 경보가 발생했습니다. 감지기 점검 및 재설정 필요합니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>지하주차장 B2 구역 배수구 주변에 물이 고여 차량 통행 시 미끄럼 위험이 있습니다. 배수관 막힘 여부 확인 요청드립니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MRI 장비실 내부 온도가 기준치보다 높게 유지되고 있습니다. 장비 보호를 위해 냉방기 작동 상태 점검 바랍니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>3병동 복도 일부 LED 조명이 점등되지 않아 야간 근무 시 시야 확보가 어렵습니다. 조명 교체 요청드립니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>응급실 출입 자동문이 환자 침대 이동 시 반응이 늦어 충돌 위험이 있습니다. 센서 감도 및 모터 상태 점검이 필요합니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>전기/통신</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>aircon.png</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -365,10 +391,20 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>처리시간</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>처리 내용</t>
+  </si>
+  <si>
     <t>이중앙</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>냉매 점검 및 수리 완료</t>
+  </si>
+  <si>
     <t>오관리</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -381,6 +417,12 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>온수 모듈 교체 완료</t>
+  </si>
+  <si>
+    <t>LED 조명으로 교체 완료</t>
+  </si>
+  <si>
     <t>최전기</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -393,6 +435,9 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>점검 완료</t>
+  </si>
+  <si>
     <t>강통신</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -405,36 +450,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>처리시간</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>디지털전략팀</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>기계/소방</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>접수</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>본관</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>엘리베이터 고장</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>4호기 문이 안열립니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>번호</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>점검 및 조치 완료</t>
   </si>
 </sst>
 </file>
@@ -444,7 +460,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-409]yy&quot;-&quot;m&quot;-&quot;d\ h:mm\ AM/PM;@"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -518,7 +534,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -527,18 +543,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -554,9 +568,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -594,9 +608,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -629,26 +643,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -681,26 +678,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -875,27 +855,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I27"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="4" max="4" width="18.75" customWidth="1"/>
     <col min="9" max="9" width="16.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
@@ -910,7 +890,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="A2">
         <v>1</v>
       </c>
@@ -918,25 +898,25 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="I2" s="2">
         <v>46082.375</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3">
         <v>2</v>
       </c>
@@ -944,54 +924,54 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="G3" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="I3" s="2">
         <v>46124.5</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="I4" s="2">
         <v>46054.625</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9">
       <c r="A5">
         <v>4</v>
       </c>
@@ -999,51 +979,51 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="H5" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="I5" s="2">
         <v>46082.75</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="H6" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="I6" s="2">
         <v>46082.875</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1051,539 +1031,539 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" t="s">
         <v>20</v>
-      </c>
-      <c r="D7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" t="s">
-        <v>65</v>
-      </c>
-      <c r="H7" t="s">
-        <v>79</v>
       </c>
       <c r="I7" s="2">
         <v>46024</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
-        <v>101</v>
+        <v>42</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="H8" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="I8" s="2">
         <v>46030.032638888886</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="H9" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="I9" s="2">
         <v>45728.032638888886</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="F10" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="H10" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="I10" s="2">
         <v>45727.032638888886</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="F11" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H11" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="I11" s="2">
         <v>45699.032638888886</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="F12" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H12" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="I12" s="2">
         <v>45700.032638888886</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="F13" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H13" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="I13" s="2">
         <v>45701.032638888886</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="F14" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H14" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="I14" s="2">
         <v>45361.032638888886</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="F15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H15" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="I15" s="2">
         <v>45360.032638888886</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="D16" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="F16" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H16" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="I16" s="2">
         <v>45331.032638888886</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="E17" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="F17" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="H17" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="I17" s="2">
         <v>45330.032638888886</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="E18" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="F18" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H18" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="I18" s="2">
         <v>45332.03402777778</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="E19" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="F19" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H19" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="I19" s="2">
         <v>45329.03402777778</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D20" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="F20" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="H20" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="I20" s="2">
         <v>45303.03402777778</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="E21" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="F21" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="H21" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="I21" s="2">
         <v>45304.03402777778</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="E22" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="F22" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="H22" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="I22" s="2">
         <v>45297.03402777778</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="E23" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="F23" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="I23" s="2">
         <v>45301.03402777778</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="E24" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="F24" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="H24" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="I24" s="2">
         <v>45301.03402777778</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="C25" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="E25" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="F25" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="H25" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="I25" s="2">
         <v>45301.03402777778</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D26" t="s">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="E26" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="F26" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="H26" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="I26" s="2">
         <v>46091.03402777778</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D27" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="E27" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="F27" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="H27" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="I27" s="2">
         <v>46120.625</v>
@@ -1599,298 +1579,281 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{011A9EEE-03A3-4373-97D5-C87F85303DEA}">
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="3" max="3" width="31.125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="31.125" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>116</v>
+        <v>106</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="3"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="5"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C2" s="5"/>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C3" s="2">
         <v>46125.5</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="5"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+      <c r="C4" s="5"/>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="5"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+      <c r="C5" s="5"/>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C6" s="7">
+        <v>113</v>
+      </c>
+      <c r="C6" s="6">
         <v>46091.875</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C7" s="6">
+        <v>111</v>
+      </c>
+      <c r="C7" s="5">
         <v>46025</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+      <c r="C8" s="5"/>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="5"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+      <c r="C9" s="5"/>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+      <c r="C10" s="5"/>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="3">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+      <c r="C11" s="5"/>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="3">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+      <c r="C12" s="5"/>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="3">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C13" s="6">
+        <v>117</v>
+      </c>
+      <c r="C13" s="5">
         <v>45703.449305555558</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="3">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+      <c r="C14" s="5"/>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" s="3">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C15" s="7">
+        <v>112</v>
+      </c>
+      <c r="C15" s="6">
         <v>45361.490972222222</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="3">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C16" s="7">
+        <v>120</v>
+      </c>
+      <c r="C16" s="6">
         <v>45333.407638888886</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D16" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" s="3">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D17" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" s="3">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="5"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+      <c r="C18" s="5"/>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" s="3">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C19" s="6">
+        <v>116</v>
+      </c>
+      <c r="C19" s="5">
         <v>45330.03402777778</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" s="3">
         <v>19</v>
       </c>
       <c r="B20" s="3"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C20" s="5"/>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" s="3">
         <v>20</v>
       </c>
       <c r="B21" s="3"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="5"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C21" s="5"/>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" s="3">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="5"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+      <c r="C22" s="5"/>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" s="3">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="5"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+      <c r="C23" s="5"/>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" s="3">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="5"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+      <c r="C24" s="5"/>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" s="3">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="5"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+      <c r="C25" s="5"/>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" s="3">
         <v>25</v>
       </c>
       <c r="B26" s="3"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="5"/>
+      <c r="C26" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
